--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_DAMEX CB ALGECIRAS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_DAMEX CB ALGECIRAS.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>B. GARCIA ALVAREZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>122.4899</v>
+        <v>127.6335</v>
       </c>
       <c r="E2" t="n">
-        <v>72.1153</v>
+        <v>86.6413</v>
       </c>
       <c r="F2" t="n">
-        <v>50.3748</v>
+        <v>40.9922</v>
       </c>
       <c r="G2" t="n">
-        <v>27.3381</v>
+        <v>67.2651</v>
       </c>
       <c r="H2" t="n">
-        <v>8.370900000000001</v>
+        <v>25.8707</v>
       </c>
       <c r="I2" t="n">
-        <v>18.9668</v>
+        <v>41.3939</v>
       </c>
       <c r="J2" t="n">
-        <v>39.3721</v>
+        <v>86.8047</v>
       </c>
       <c r="K2" t="n">
-        <v>22.3211</v>
+        <v>45.7379</v>
       </c>
       <c r="L2" t="n">
-        <v>17.051</v>
+        <v>41.0668</v>
       </c>
       <c r="M2" t="n">
-        <v>-12.0345</v>
+        <v>-19.5399</v>
       </c>
       <c r="N2" t="n">
-        <v>-13.95</v>
+        <v>-19.8671</v>
       </c>
       <c r="O2" t="n">
-        <v>1.9162</v>
+        <v>0.3272000000000004</v>
       </c>
       <c r="P2" t="n">
-        <v>17.4437</v>
+        <v>16.2541</v>
       </c>
       <c r="Q2" t="n">
-        <v>-33.1029</v>
+        <v>-50.7451</v>
       </c>
       <c r="R2" t="n">
-        <v>50.547</v>
+        <v>66.99930000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>71.7884</v>
+        <v>11.5386</v>
       </c>
       <c r="T2" t="n">
-        <v>48.1773</v>
+        <v>5.878</v>
       </c>
       <c r="U2" t="n">
-        <v>23.6111</v>
+        <v>5.6602</v>
       </c>
       <c r="V2" t="n">
-        <v>5.920000000000001</v>
+        <v>32.5757</v>
       </c>
       <c r="W2" t="n">
-        <v>17.6692</v>
+        <v>44.7035</v>
       </c>
       <c r="X2" t="n">
-        <v>-11.7493</v>
+        <v>-12.1275</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>118.0702</v>
+        <v>103.718</v>
       </c>
       <c r="E3" t="n">
-        <v>68.6829</v>
+        <v>56.3657</v>
       </c>
       <c r="F3" t="n">
-        <v>49.3872</v>
+        <v>47.3526</v>
       </c>
       <c r="G3" t="n">
         <v>38.6556</v>
@@ -688,13 +688,13 @@
         <v>68.3867</v>
       </c>
       <c r="S3" t="n">
-        <v>39.3093</v>
+        <v>24.9575</v>
       </c>
       <c r="T3" t="n">
-        <v>26.773</v>
+        <v>14.4557</v>
       </c>
       <c r="U3" t="n">
-        <v>12.5364</v>
+        <v>10.5015</v>
       </c>
       <c r="V3" t="n">
         <v>15.5253</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. GARCIA ALVAREZ</t>
+          <t>B. EDOKPAYI MANCERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>107.1337</v>
+        <v>88.2651</v>
       </c>
       <c r="E4" t="n">
-        <v>70.1062</v>
+        <v>67.8693</v>
       </c>
       <c r="F4" t="n">
-        <v>37.0275</v>
+        <v>20.3958</v>
       </c>
       <c r="G4" t="n">
-        <v>67.2651</v>
+        <v>34.9546</v>
       </c>
       <c r="H4" t="n">
-        <v>25.8707</v>
+        <v>9.8811</v>
       </c>
       <c r="I4" t="n">
-        <v>41.3939</v>
+        <v>25.0732</v>
       </c>
       <c r="J4" t="n">
-        <v>86.8047</v>
+        <v>67.7102</v>
       </c>
       <c r="K4" t="n">
-        <v>45.7379</v>
+        <v>31.2612</v>
       </c>
       <c r="L4" t="n">
-        <v>41.0668</v>
+        <v>36.4489</v>
       </c>
       <c r="M4" t="n">
-        <v>-19.5399</v>
+        <v>-32.7557</v>
       </c>
       <c r="N4" t="n">
-        <v>-19.8671</v>
+        <v>-21.3797</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3272000000000004</v>
+        <v>-11.3759</v>
       </c>
       <c r="P4" t="n">
-        <v>16.2541</v>
+        <v>13.2808</v>
       </c>
       <c r="Q4" t="n">
-        <v>-50.7451</v>
+        <v>-53.3217</v>
       </c>
       <c r="R4" t="n">
-        <v>66.99930000000001</v>
+        <v>66.6032</v>
       </c>
       <c r="S4" t="n">
-        <v>-8.9612</v>
+        <v>14.782</v>
       </c>
       <c r="T4" t="n">
-        <v>-10.6563</v>
+        <v>10.0703</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6952</v>
+        <v>4.711</v>
       </c>
       <c r="V4" t="n">
-        <v>32.5757</v>
+        <v>25.2479</v>
       </c>
       <c r="W4" t="n">
-        <v>44.7035</v>
+        <v>43.4107</v>
       </c>
       <c r="X4" t="n">
-        <v>-12.1275</v>
+        <v>-18.1629</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. EDOKPAYI MANCERA</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>75.8488</v>
+        <v>86.4449</v>
       </c>
       <c r="E5" t="n">
-        <v>59.8586</v>
+        <v>46.2199</v>
       </c>
       <c r="F5" t="n">
-        <v>15.9905</v>
+        <v>40.2253</v>
       </c>
       <c r="G5" t="n">
-        <v>34.9546</v>
+        <v>27.3381</v>
       </c>
       <c r="H5" t="n">
-        <v>9.8811</v>
+        <v>8.370900000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>25.0732</v>
+        <v>18.9668</v>
       </c>
       <c r="J5" t="n">
-        <v>67.7102</v>
+        <v>39.3721</v>
       </c>
       <c r="K5" t="n">
-        <v>31.2612</v>
+        <v>22.3211</v>
       </c>
       <c r="L5" t="n">
-        <v>36.4489</v>
+        <v>17.051</v>
       </c>
       <c r="M5" t="n">
-        <v>-32.7557</v>
+        <v>-12.0345</v>
       </c>
       <c r="N5" t="n">
-        <v>-21.3797</v>
+        <v>-13.95</v>
       </c>
       <c r="O5" t="n">
-        <v>-11.3759</v>
+        <v>1.9162</v>
       </c>
       <c r="P5" t="n">
-        <v>13.2808</v>
+        <v>17.4437</v>
       </c>
       <c r="Q5" t="n">
-        <v>-53.3217</v>
+        <v>-33.1029</v>
       </c>
       <c r="R5" t="n">
-        <v>66.6032</v>
+        <v>50.547</v>
       </c>
       <c r="S5" t="n">
-        <v>2.3659</v>
+        <v>35.7437</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0599</v>
+        <v>22.2817</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3062000000000001</v>
+        <v>13.4616</v>
       </c>
       <c r="V5" t="n">
-        <v>25.2479</v>
+        <v>5.920000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>43.4107</v>
+        <v>17.6692</v>
       </c>
       <c r="X5" t="n">
-        <v>-18.1629</v>
+        <v>-11.7493</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>66.6161</v>
+        <v>84.795</v>
       </c>
       <c r="E6" t="n">
-        <v>48.9773</v>
+        <v>59.5117</v>
       </c>
       <c r="F6" t="n">
-        <v>17.6391</v>
+        <v>25.2831</v>
       </c>
       <c r="G6" t="n">
         <v>58.8811</v>
@@ -922,13 +922,13 @@
         <v>56.0974</v>
       </c>
       <c r="S6" t="n">
-        <v>-16.647</v>
+        <v>1.5316</v>
       </c>
       <c r="T6" t="n">
-        <v>-9.2948</v>
+        <v>1.24</v>
       </c>
       <c r="U6" t="n">
-        <v>-7.3521</v>
+        <v>0.2919</v>
       </c>
       <c r="V6" t="n">
         <v>12.885</v>
@@ -955,13 +955,13 @@
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>43.2715</v>
+        <v>33.4618</v>
       </c>
       <c r="E7" t="n">
-        <v>34.1021</v>
+        <v>26.2706</v>
       </c>
       <c r="F7" t="n">
-        <v>9.1698</v>
+        <v>7.1912</v>
       </c>
       <c r="G7" t="n">
         <v>14.4001</v>
@@ -1000,13 +1000,13 @@
         <v>18.8312</v>
       </c>
       <c r="S7" t="n">
-        <v>18.8369</v>
+        <v>9.026999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>13.8407</v>
+        <v>6.0096</v>
       </c>
       <c r="U7" t="n">
-        <v>4.9962</v>
+        <v>3.0177</v>
       </c>
       <c r="V7" t="n">
         <v>12.4131</v>
@@ -1033,13 +1033,13 @@
         <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>24.8188</v>
+        <v>28.0492</v>
       </c>
       <c r="E8" t="n">
-        <v>8.017399999999999</v>
+        <v>13.2547</v>
       </c>
       <c r="F8" t="n">
-        <v>16.8013</v>
+        <v>14.7948</v>
       </c>
       <c r="G8" t="n">
         <v>1.9043</v>
@@ -1078,13 +1078,13 @@
         <v>45.5911</v>
       </c>
       <c r="S8" t="n">
-        <v>2.321</v>
+        <v>5.551600000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-3.1762</v>
+        <v>2.0613</v>
       </c>
       <c r="U8" t="n">
-        <v>5.4969</v>
+        <v>3.4904</v>
       </c>
       <c r="V8" t="n">
         <v>-4.779199999999999</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. PAÑOS HUERTAS</t>
+          <t>A. ARTILES AGUILAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>9.056100000000001</v>
+        <v>22.4243</v>
       </c>
       <c r="E9" t="n">
-        <v>9.056100000000001</v>
+        <v>6.899299999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>15.5252</v>
       </c>
       <c r="G9" t="n">
-        <v>9.056100000000001</v>
+        <v>-4.2085</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6322</v>
+        <v>-7.932300000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>5.4241</v>
+        <v>3.7239</v>
       </c>
       <c r="J9" t="n">
-        <v>9.056100000000001</v>
+        <v>16.7038</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6322</v>
+        <v>9.502800000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>5.4241</v>
+        <v>7.200900000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-20.9124</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-17.4352</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-3.4772</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>21.2099</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-26.3634</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>47.5736</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>8.282500000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.7031</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>4.5793</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.859900000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>12.8558</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-15.7157</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ARTILES AGUILAR</t>
+          <t>E. EGEA SOLER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>9.014900000000001</v>
+        <v>11.3072</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.938899999999999</v>
+        <v>3.747699999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>11.9539</v>
+        <v>7.5594</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.2085</v>
+        <v>0.6880000000000015</v>
       </c>
       <c r="H10" t="n">
-        <v>-7.932300000000001</v>
+        <v>-10.3153</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7239</v>
+        <v>11.0036</v>
       </c>
       <c r="J10" t="n">
-        <v>16.7038</v>
+        <v>17.6108</v>
       </c>
       <c r="K10" t="n">
-        <v>9.502800000000001</v>
+        <v>3.8207</v>
       </c>
       <c r="L10" t="n">
-        <v>7.200900000000001</v>
+        <v>13.7901</v>
       </c>
       <c r="M10" t="n">
-        <v>-20.9124</v>
+        <v>-16.9229</v>
       </c>
       <c r="N10" t="n">
-        <v>-17.4352</v>
+        <v>-14.136</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.4772</v>
+        <v>-2.7865</v>
       </c>
       <c r="P10" t="n">
-        <v>21.2099</v>
+        <v>4.3606</v>
       </c>
       <c r="Q10" t="n">
-        <v>-26.3634</v>
+        <v>-40.6355</v>
       </c>
       <c r="R10" t="n">
-        <v>47.5736</v>
+        <v>44.9969</v>
       </c>
       <c r="S10" t="n">
-        <v>-5.1267</v>
+        <v>0.6178000000000002</v>
       </c>
       <c r="T10" t="n">
-        <v>-6.1349</v>
+        <v>3.1233</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0082</v>
+        <v>-2.5052</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.859900000000001</v>
+        <v>5.6402</v>
       </c>
       <c r="W10" t="n">
-        <v>12.8558</v>
+        <v>23.6494</v>
       </c>
       <c r="X10" t="n">
-        <v>-15.7157</v>
+        <v>-18.0092</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MONTENEGRO MOYA</t>
+          <t>L. PAÑOS HUERTAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>2.3478</v>
+        <v>9.056100000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.03979999999999984</v>
+        <v>9.056100000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3876</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8633999999999997</v>
+        <v>9.056100000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7637</v>
+        <v>3.6322</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09959999999999997</v>
+        <v>5.4241</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9530000000000002</v>
+        <v>9.056100000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9961999999999998</v>
+        <v>3.6322</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9492</v>
+        <v>5.4241</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8164</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2325</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.0488</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7839</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9732</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.5879</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1819</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.4062</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>2.2885</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.2844</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.9959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. CALDERON QUINONES</t>
+          <t>A. MONTENEGRO MOYA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>2.2744</v>
+        <v>4.2337</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3829</v>
+        <v>1.2845</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8916000000000002</v>
+        <v>2.9492</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6869</v>
+        <v>0.8633999999999997</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3684</v>
+        <v>0.7637</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3183</v>
+        <v>0.09959999999999997</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8684</v>
+        <v>-0.9530000000000002</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7201</v>
+        <v>0.9961999999999998</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1483</v>
+        <v>-1.9492</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8186</v>
+        <v>1.8164</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6485000000000001</v>
+        <v>-0.2325</v>
       </c>
       <c r="O12" t="n">
-        <v>0.17</v>
+        <v>2.0488</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3966000000000001</v>
+        <v>1.7839</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.9644</v>
+        <v>-1.1893</v>
       </c>
       <c r="R12" t="n">
-        <v>3.5678</v>
+        <v>2.9732</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8572</v>
+        <v>-0.7020000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1946999999999999</v>
+        <v>0.1425</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6625</v>
+        <v>-0.8446</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8730999999999999</v>
+        <v>2.2885</v>
       </c>
       <c r="W12" t="n">
         <v>3.2844</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.157500000000001</v>
+        <v>-0.9959</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. CALDERON QUIÑONES</t>
+          <t>R. CALDERON QUINONES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2054</v>
+        <v>3.5289</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2054</v>
+        <v>2.894500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.6344</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2054</v>
+        <v>2.6869</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1.3684</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2054</v>
+        <v>1.3183</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2054</v>
+        <v>1.8684</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.7201</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2054</v>
+        <v>1.1483</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>0.8186</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.6485000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0.3966000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-3.9644</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.5678</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.1115</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.7063</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.4051999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.8730999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.2844</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-4.157500000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. RODRIGUEZ SOLER</t>
+          <t>R. CALDERON QUIÑONES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,58 +1501,58 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5692</v>
+        <v>1.2054</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0005000000000000004</v>
+        <v>1.2054</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5697</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7017</v>
+        <v>1.2054</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5207000000000001</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2224</v>
+        <v>1.2054</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.1092</v>
+        <v>1.2054</v>
       </c>
       <c r="K14" t="n">
-        <v>0.249</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.3583</v>
+        <v>1.2054</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4075</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2717</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1358</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0727</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1087</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.036</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4651</v>
+        <v>0.6231</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0422</v>
+        <v>0.0596</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5073</v>
+        <v>0.5635</v>
       </c>
       <c r="G15" t="n">
         <v>0.4277</v>
@@ -1624,13 +1624,13 @@
         <v>0.1982</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1608</v>
+        <v>-0.0028</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0984</v>
+        <v>-0.0422</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. EGEA SOLER</t>
+          <t>I. RODRIGUEZ SOLER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1206999999999985</v>
+        <v>0.0765</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5395999999999996</v>
+        <v>-0.5494</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6603000000000008</v>
+        <v>0.6259</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6880000000000015</v>
+        <v>-0.7017</v>
       </c>
       <c r="H18" t="n">
-        <v>-10.3153</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>11.0036</v>
+        <v>-1.2224</v>
       </c>
       <c r="J18" t="n">
-        <v>17.6108</v>
+        <v>-1.1092</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8207</v>
+        <v>0.249</v>
       </c>
       <c r="L18" t="n">
-        <v>13.7901</v>
+        <v>-1.3583</v>
       </c>
       <c r="M18" t="n">
-        <v>-16.9229</v>
+        <v>0.4075</v>
       </c>
       <c r="N18" t="n">
-        <v>-14.136</v>
+        <v>0.2717</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.7865</v>
+        <v>0.1358</v>
       </c>
       <c r="P18" t="n">
-        <v>4.3606</v>
+        <v>0.1982</v>
       </c>
       <c r="Q18" t="n">
-        <v>-40.6355</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>44.9969</v>
+        <v>0.1982</v>
       </c>
       <c r="S18" t="n">
-        <v>-10.5685</v>
+        <v>0.58</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1643</v>
+        <v>0.5598</v>
       </c>
       <c r="U18" t="n">
-        <v>-9.404500000000001</v>
+        <v>0.0202</v>
       </c>
       <c r="V18" t="n">
-        <v>5.6402</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>23.6494</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-18.0092</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3755</v>
+        <v>-0.3193</v>
       </c>
       <c r="E19" t="n">
         <v>-0.681</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3055</v>
+        <v>0.3617</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5487</v>
@@ -1936,13 +1936,13 @@
         <v>0.1982</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.025</v>
+        <v>0.0312</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0624</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0374</v>
+        <v>0.0936</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. NGOM</t>
+          <t>J. CALDERON QUINONES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6531999999999991</v>
+        <v>-0.4669</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0401</v>
+        <v>0.1615</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6933</v>
+        <v>-0.6284</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.7421</v>
+        <v>0.1599</v>
       </c>
       <c r="H20" t="n">
-        <v>-6.0063</v>
+        <v>0.0241</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2644</v>
+        <v>0.1358</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3991999999999998</v>
+        <v>0.0202</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4362</v>
+        <v>0.0202</v>
       </c>
       <c r="L20" t="n">
-        <v>1.8354</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-5.1412</v>
+        <v>0.1398</v>
       </c>
       <c r="N20" t="n">
-        <v>-4.5702</v>
+        <v>0.0039</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5707</v>
+        <v>0.1358</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9734</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-7.7306</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>10.704</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.9984</v>
+        <v>-0.6268</v>
       </c>
       <c r="T20" t="n">
-        <v>4.3581</v>
+        <v>0.1413</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3597</v>
+        <v>-0.7682</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.883</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>4.0136</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-6.8966</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6949</v>
+        <v>-0.7792</v>
       </c>
       <c r="E21" t="n">
         <v>-1.1494</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4544</v>
+        <v>0.3702</v>
       </c>
       <c r="G21" t="n">
         <v>0.0404</v>
@@ -2092,13 +2092,13 @@
         <v>0.3964</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1406</v>
+        <v>-0.2249</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1248</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0158</v>
+        <v>-0.1001</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CALDERON QUINONES</t>
+          <t>K. VAN BRANDWIJK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,61 +2122,61 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6987</v>
+        <v>-1.6542</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0422</v>
+        <v>-2.4346</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6565</v>
+        <v>0.7804</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1599</v>
+        <v>-0.9007999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0241</v>
+        <v>-1.314</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1358</v>
+        <v>0.4132</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0202</v>
+        <v>-1.318</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0202</v>
+        <v>-1.318</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1398</v>
+        <v>0.4172</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0039</v>
+        <v>0.003900000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1358</v>
+        <v>0.4132</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8586</v>
+        <v>-0.357</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0624</v>
+        <v>-0.1257</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7962</v>
+        <v>-0.2313</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. VAN BRANDWIJK</t>
+          <t>E. NGOM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2200,70 +2200,70 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3486</v>
+        <v>-2.8062</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.129</v>
+        <v>-1.585599999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7804</v>
+        <v>-1.2206</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9007999999999999</v>
+        <v>-4.7421</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.314</v>
+        <v>-6.0063</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4132</v>
+        <v>1.2644</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.318</v>
+        <v>0.3991999999999998</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.318</v>
+        <v>-1.4362</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.8354</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4172</v>
+        <v>-5.1412</v>
       </c>
       <c r="N23" t="n">
-        <v>0.003900000000000001</v>
+        <v>-4.5702</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4132</v>
+        <v>-0.5707</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3964</v>
+        <v>2.9734</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9911</v>
+        <v>-7.7306</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5947</v>
+        <v>10.704</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0513</v>
+        <v>1.8454</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1799</v>
+        <v>1.7326</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2313</v>
+        <v>0.1132</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.883</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>4.0136</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-6.8966</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2116</v>
+        <v>-2.9798</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4019</v>
+        <v>-4.1982</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1902</v>
+        <v>1.2183</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9082</v>
@@ -2326,13 +2326,13 @@
         <v>1.1893</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1545</v>
+        <v>0.3864</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1762</v>
+        <v>0.0276</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3307</v>
+        <v>0.3588</v>
       </c>
       <c r="V24" t="n">
         <v>-0.674</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>K. DOMINGOS</t>
+          <t>A. PEREZ PENA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2356,76 +2356,76 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.9514</v>
+        <v>-4.800800000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.1969</v>
+        <v>-6.6362</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.7547</v>
+        <v>1.8352</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.1148</v>
+        <v>-5.3129</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.2673</v>
+        <v>-1.1137</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8474999999999999</v>
+        <v>-4.1992</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6794</v>
+        <v>-5.0762</v>
       </c>
       <c r="K25" t="n">
-        <v>0.599</v>
+        <v>-0.3222000000000003</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0804</v>
+        <v>-4.7539</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.7943</v>
+        <v>-0.2367</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.8663</v>
+        <v>-0.7915000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9278999999999999</v>
+        <v>0.5547</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.1804</v>
+        <v>0.3964</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7928999999999999</v>
+        <v>1.3875</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5509999999999999</v>
+        <v>0.1157</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2975000000000001</v>
+        <v>-0.5688</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2534999999999999</v>
+        <v>0.6845</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.207</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0.7997000000000001</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.0068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. PEREZ PENA</t>
+          <t>K. DOMINGOS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2434,70 +2434,70 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.489100000000001</v>
+        <v>-5.4135</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.0436</v>
+        <v>-1.5419</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5546</v>
+        <v>-3.8715</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.3129</v>
+        <v>-2.1148</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.1137</v>
+        <v>-1.2673</v>
       </c>
       <c r="I26" t="n">
-        <v>-4.1992</v>
+        <v>-0.8474999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.0762</v>
+        <v>0.6794</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.3222000000000003</v>
+        <v>0.599</v>
       </c>
       <c r="L26" t="n">
-        <v>-4.7539</v>
+        <v>0.0804</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2367</v>
+        <v>-2.7943</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.7915000000000001</v>
+        <v>-1.8663</v>
       </c>
       <c r="O26" t="n">
-        <v>0.5547</v>
+        <v>-0.9278999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>0.3964</v>
+        <v>-2.1804</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3875</v>
+        <v>0.7928999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5726</v>
+        <v>0.0891</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9763000000000001</v>
+        <v>-0.0476</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4037</v>
+        <v>0.1367</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>-1.207</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.7997000000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>-2.0068</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>-7.3912</v>
+        <v>-5.8183</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.2621</v>
+        <v>-2.7735</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.1291</v>
+        <v>-3.0447</v>
       </c>
       <c r="G27" t="n">
         <v>-2.021100000000001</v>
@@ -2560,13 +2560,13 @@
         <v>2.1804</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.6803</v>
+        <v>-0.1074</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.8735999999999999</v>
+        <v>0.6148</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.8068</v>
+        <v>-0.7224999999999999</v>
       </c>
       <c r="V27" t="n">
         <v>-3.8878</v>
@@ -2593,13 +2593,13 @@
         <v>16</v>
       </c>
       <c r="D28" t="n">
-        <v>-15.7978</v>
+        <v>-12.1776</v>
       </c>
       <c r="E28" t="n">
-        <v>-18.7732</v>
+        <v>-17.2551</v>
       </c>
       <c r="F28" t="n">
-        <v>2.9756</v>
+        <v>5.077500000000001</v>
       </c>
       <c r="G28" t="n">
         <v>-4.4182</v>
@@ -2638,13 +2638,13 @@
         <v>19.4257</v>
       </c>
       <c r="S28" t="n">
-        <v>3.7336</v>
+        <v>7.3534</v>
       </c>
       <c r="T28" t="n">
-        <v>3.3783</v>
+        <v>4.8963</v>
       </c>
       <c r="U28" t="n">
-        <v>0.3551000000000001</v>
+        <v>2.4574</v>
       </c>
       <c r="V28" t="n">
         <v>-14.7168</v>
@@ -2671,13 +2671,13 @@
         <v>26</v>
       </c>
       <c r="D29" t="n">
-        <v>543.2959999999999</v>
+        <v>568.2123</v>
       </c>
       <c r="E29" t="n">
-        <v>331.9094000000001</v>
+        <v>343.2422999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>211.3877</v>
+        <v>224.9707</v>
       </c>
       <c r="G29" t="n">
         <v>233.2551</v>
@@ -2689,7 +2689,7 @@
         <v>181.5311</v>
       </c>
       <c r="J29" t="n">
-        <v>406.7957000000001</v>
+        <v>406.7957</v>
       </c>
       <c r="K29" t="n">
         <v>207.191</v>
@@ -2713,16 +2713,16 @@
         <v>-377.6131</v>
       </c>
       <c r="R29" t="n">
-        <v>509.4329000000001</v>
+        <v>509.4329</v>
       </c>
       <c r="S29" t="n">
-        <v>97.6084</v>
+        <v>122.5241</v>
       </c>
       <c r="T29" t="n">
-        <v>66.42159999999998</v>
+        <v>77.75439999999999</v>
       </c>
       <c r="U29" t="n">
-        <v>31.1861</v>
+        <v>44.76910000000001</v>
       </c>
       <c r="V29" t="n">
         <v>80.61490000000001</v>
